--- a/proposed/results/training_tables/suburban_training_results.xlsx
+++ b/proposed/results/training_tables/suburban_training_results.xlsx
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9243.329100000001</v>
+        <v>8258.077300000001</v>
       </c>
       <c r="C2" t="n">
-        <v>184.8666</v>
+        <v>165.1615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5542</v>
+        <v>0.8535</v>
       </c>
     </row>
     <row r="3">
@@ -467,10 +467,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>10373.9946</v>
+        <v>7943.7193</v>
       </c>
       <c r="C3" t="n">
-        <v>207.4799</v>
+        <v>158.8744</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0578</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="4">
@@ -486,10 +486,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>7341.6668</v>
+        <v>4391.1297</v>
       </c>
       <c r="C4" t="n">
-        <v>146.8333</v>
+        <v>87.82259999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0551</v>
+        <v>0.0636</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>10307.8636</v>
+        <v>5689.8667</v>
       </c>
       <c r="C5" t="n">
-        <v>206.1573</v>
+        <v>113.7973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0576</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8870.940699999999</v>
+        <v>6054.553</v>
       </c>
       <c r="C6" t="n">
-        <v>177.4188</v>
+        <v>121.0911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1754</v>
+        <v>0.1814</v>
       </c>
     </row>
     <row r="7">
@@ -543,10 +543,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>9341.908799999999</v>
+        <v>5786.1501</v>
       </c>
       <c r="C7" t="n">
-        <v>186.8382</v>
+        <v>115.723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0554</v>
+        <v>0.0579</v>
       </c>
     </row>
     <row r="8">
@@ -562,10 +562,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>9306.7721</v>
+        <v>5297.3807</v>
       </c>
       <c r="C8" t="n">
-        <v>186.1354</v>
+        <v>105.9476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0566</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="9">
@@ -581,10 +581,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7241.7197</v>
+        <v>2254.4229</v>
       </c>
       <c r="C9" t="n">
-        <v>144.8344</v>
+        <v>45.0885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0514</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="10">
@@ -600,10 +600,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>10340.0423</v>
+        <v>5369.8364</v>
       </c>
       <c r="C10" t="n">
-        <v>206.8008</v>
+        <v>107.3967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.1704</v>
+        <v>0.2035</v>
       </c>
     </row>
     <row r="11">
@@ -619,10 +619,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>8353.4323</v>
+        <v>5174.7992</v>
       </c>
       <c r="C11" t="n">
-        <v>167.0686</v>
+        <v>103.496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0567</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="12">
@@ -638,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>7354.5473</v>
+        <v>3252.5267</v>
       </c>
       <c r="C12" t="n">
-        <v>147.0909</v>
+        <v>65.0505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0507</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="13">
@@ -657,10 +657,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>8540.9481</v>
+        <v>5539.5565</v>
       </c>
       <c r="C13" t="n">
-        <v>170.819</v>
+        <v>110.7911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0514</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="14">
@@ -676,10 +676,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>8518.982099999999</v>
+        <v>5238.7721</v>
       </c>
       <c r="C14" t="n">
-        <v>170.3796</v>
+        <v>104.7754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.1513</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="15">
@@ -695,10 +695,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>8275.7858</v>
+        <v>4234.7264</v>
       </c>
       <c r="C15" t="n">
-        <v>165.5157</v>
+        <v>84.69450000000001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0573</v>
+        <v>0.0611</v>
       </c>
     </row>
     <row r="16">
@@ -714,10 +714,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>7848.1248</v>
+        <v>2845.4779</v>
       </c>
       <c r="C16" t="n">
-        <v>156.9625</v>
+        <v>56.9096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0505</v>
+        <v>0.0554</v>
       </c>
     </row>
     <row r="17">
@@ -733,10 +733,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>8442.3539</v>
+        <v>5841.913</v>
       </c>
       <c r="C17" t="n">
-        <v>168.8471</v>
+        <v>116.8383</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0638</v>
+        <v>0.0633</v>
       </c>
     </row>
     <row r="18">
@@ -752,10 +752,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>10027.4357</v>
+        <v>7126.5961</v>
       </c>
       <c r="C18" t="n">
-        <v>200.5487</v>
+        <v>142.5319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.1493</v>
+        <v>0.1832</v>
       </c>
     </row>
     <row r="19">
@@ -771,10 +771,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>8153.9983</v>
+        <v>3643.2917</v>
       </c>
       <c r="C19" t="n">
-        <v>163.08</v>
+        <v>72.86579999999999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0563</v>
+        <v>0.0579</v>
       </c>
     </row>
     <row r="20">
@@ -790,10 +790,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>7213.306</v>
+        <v>2210.2616</v>
       </c>
       <c r="C20" t="n">
-        <v>144.2661</v>
+        <v>44.2052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0526</v>
+        <v>0.0548</v>
       </c>
     </row>
     <row r="21">
@@ -809,10 +809,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>8732.567999999999</v>
+        <v>5066.6362</v>
       </c>
       <c r="C21" t="n">
-        <v>174.6514</v>
+        <v>101.3327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0477</v>
+        <v>0.0607</v>
       </c>
     </row>
     <row r="22">
@@ -828,10 +828,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>8771.401</v>
+        <v>5487.2963</v>
       </c>
       <c r="C22" t="n">
-        <v>175.428</v>
+        <v>109.7459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.1538</v>
+        <v>0.1854</v>
       </c>
     </row>
     <row r="23">
@@ -847,10 +847,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>10754.4795</v>
+        <v>7067.7837</v>
       </c>
       <c r="C23" t="n">
-        <v>215.0896</v>
+        <v>141.3557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0519</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="24">
@@ -866,10 +866,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>11623.9271</v>
+        <v>7681.7176</v>
       </c>
       <c r="C24" t="n">
-        <v>232.4785</v>
+        <v>153.6344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0497</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="25">
@@ -885,10 +885,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>11139.0718</v>
+        <v>7176.7618</v>
       </c>
       <c r="C25" t="n">
-        <v>222.7814</v>
+        <v>143.5352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0496</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="26">
@@ -904,10 +904,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>11373.2395</v>
+        <v>5924.9264</v>
       </c>
       <c r="C26" t="n">
-        <v>227.4648</v>
+        <v>118.4985</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.1694</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="27">
@@ -923,10 +923,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>7732.7162</v>
+        <v>3429.4245</v>
       </c>
       <c r="C27" t="n">
-        <v>154.6543</v>
+        <v>68.5885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0552</v>
+        <v>0.0559</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>9910.7022</v>
+        <v>4736.9774</v>
       </c>
       <c r="C28" t="n">
-        <v>198.214</v>
+        <v>94.73950000000001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0591</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="29">
@@ -961,10 +961,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>7590.9527</v>
+        <v>3537.1058</v>
       </c>
       <c r="C29" t="n">
-        <v>151.8191</v>
+        <v>70.74209999999999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0542</v>
+        <v>0.0559</v>
       </c>
     </row>
     <row r="30">
@@ -980,10 +980,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>8332.6432</v>
+        <v>5199.8088</v>
       </c>
       <c r="C30" t="n">
-        <v>166.6529</v>
+        <v>103.9962</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.1719</v>
+        <v>0.1666</v>
       </c>
     </row>
     <row r="31">
@@ -999,10 +999,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>7994.8184</v>
+        <v>4183.8828</v>
       </c>
       <c r="C31" t="n">
-        <v>159.8964</v>
+        <v>83.6777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.055</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="32">
@@ -1018,10 +1018,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>9241.117200000001</v>
+        <v>2295.204</v>
       </c>
       <c r="C32" t="n">
-        <v>184.8223</v>
+        <v>45.9041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0528</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="33">
@@ -1037,10 +1037,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>7749.9955</v>
+        <v>3270.2486</v>
       </c>
       <c r="C33" t="n">
-        <v>154.9999</v>
+        <v>65.405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0547</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="34">
@@ -1056,10 +1056,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>10935.383</v>
+        <v>7915.0191</v>
       </c>
       <c r="C34" t="n">
-        <v>218.7077</v>
+        <v>158.3004</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.173</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="35">
@@ -1075,10 +1075,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7743.9127</v>
+        <v>4428.6023</v>
       </c>
       <c r="C35" t="n">
-        <v>154.8783</v>
+        <v>88.572</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0592</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="36">
@@ -1094,10 +1094,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>10432.9123</v>
+        <v>7229.1884</v>
       </c>
       <c r="C36" t="n">
-        <v>208.6582</v>
+        <v>144.5838</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0636</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="37">
@@ -1113,10 +1113,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>9034.663</v>
+        <v>1154.3042</v>
       </c>
       <c r="C37" t="n">
-        <v>180.6933</v>
+        <v>23.0861</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.0559</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="38">
@@ -1132,10 +1132,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>7802.3787</v>
+        <v>3188.3968</v>
       </c>
       <c r="C38" t="n">
-        <v>156.0476</v>
+        <v>63.7679</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.1592</v>
+        <v>0.1547</v>
       </c>
     </row>
     <row r="39">
@@ -1151,10 +1151,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>11842.7402</v>
+        <v>8402.0816</v>
       </c>
       <c r="C39" t="n">
-        <v>236.8548</v>
+        <v>168.0416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0682</v>
+        <v>0.0542</v>
       </c>
     </row>
     <row r="40">
@@ -1170,10 +1170,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>6991.4555</v>
+        <v>2437.3002</v>
       </c>
       <c r="C40" t="n">
-        <v>139.8291</v>
+        <v>48.746</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.059</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="41">
@@ -1189,10 +1189,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>11732.7403</v>
+        <v>7213.9964</v>
       </c>
       <c r="C41" t="n">
-        <v>234.6548</v>
+        <v>144.2799</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.0579</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="42">
@@ -1208,10 +1208,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>8640.8205</v>
+        <v>5285.7487</v>
       </c>
       <c r="C42" t="n">
-        <v>172.8164</v>
+        <v>105.715</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.1642</v>
+        <v>0.1539</v>
       </c>
     </row>
     <row r="43">
@@ -1227,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>8534.152</v>
+        <v>4580.3449</v>
       </c>
       <c r="C43" t="n">
-        <v>170.683</v>
+        <v>91.6069</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.0606</v>
+        <v>0.0498</v>
       </c>
     </row>
     <row r="44">
@@ -1246,10 +1246,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>9028.1819</v>
+        <v>2759.8051</v>
       </c>
       <c r="C44" t="n">
-        <v>180.5636</v>
+        <v>55.1961</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.0578</v>
+        <v>0.0542</v>
       </c>
     </row>
     <row r="45">
@@ -1265,10 +1265,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>9889.274299999999</v>
+        <v>4032.6913</v>
       </c>
       <c r="C45" t="n">
-        <v>197.7855</v>
+        <v>80.6538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.0534</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="46">
@@ -1284,10 +1284,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>9805.8236</v>
+        <v>6998.3934</v>
       </c>
       <c r="C46" t="n">
-        <v>196.1165</v>
+        <v>139.9679</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.1737</v>
+        <v>0.1572</v>
       </c>
     </row>
     <row r="47">
@@ -1303,10 +1303,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>9259.832700000001</v>
+        <v>5806.2793</v>
       </c>
       <c r="C47" t="n">
-        <v>185.1967</v>
+        <v>116.1256</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0644</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="48">
@@ -1322,10 +1322,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>8756.084500000001</v>
+        <v>5702.4591</v>
       </c>
       <c r="C48" t="n">
-        <v>175.1217</v>
+        <v>114.0492</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0624</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="49">
@@ -1341,10 +1341,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>10405.2069</v>
+        <v>7796.022</v>
       </c>
       <c r="C49" t="n">
-        <v>208.1041</v>
+        <v>155.9204</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0567</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="50">
@@ -1360,10 +1360,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>9935.296</v>
+        <v>7133.1444</v>
       </c>
       <c r="C50" t="n">
-        <v>198.7059</v>
+        <v>142.6629</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.1666</v>
+        <v>0.1657</v>
       </c>
     </row>
     <row r="51">
@@ -1379,10 +1379,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>12844.1611</v>
+        <v>10129.4977</v>
       </c>
       <c r="C51" t="n">
-        <v>256.8832</v>
+        <v>202.59</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0596</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="52">
@@ -1398,10 +1398,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>8571.454599999999</v>
+        <v>5365.3239</v>
       </c>
       <c r="C52" t="n">
-        <v>171.4291</v>
+        <v>107.3065</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0576</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="53">
@@ -1417,10 +1417,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>9890.769899999999</v>
+        <v>7390.7699</v>
       </c>
       <c r="C53" t="n">
-        <v>197.8154</v>
+        <v>147.8154</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0571</v>
+        <v>0.0529</v>
       </c>
     </row>
     <row r="54">
@@ -1436,10 +1436,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>9618.7407</v>
+        <v>6700.1522</v>
       </c>
       <c r="C54" t="n">
-        <v>192.3748</v>
+        <v>134.003</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.1632</v>
+        <v>0.1572</v>
       </c>
     </row>
     <row r="55">
@@ -1455,10 +1455,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>8441.470799999999</v>
+        <v>4693.1969</v>
       </c>
       <c r="C55" t="n">
-        <v>168.8294</v>
+        <v>93.8639</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.0523</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -1474,10 +1474,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>9709.4172</v>
+        <v>3922.4521</v>
       </c>
       <c r="C56" t="n">
-        <v>194.1883</v>
+        <v>78.449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0515</v>
+        <v>0.0772</v>
       </c>
     </row>
     <row r="57">
@@ -1493,10 +1493,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>11109.1181</v>
+        <v>7419.024</v>
       </c>
       <c r="C57" t="n">
-        <v>222.1824</v>
+        <v>148.3805</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0554</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="58">
@@ -1512,10 +1512,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>10065.6456</v>
+        <v>5946.6976</v>
       </c>
       <c r="C58" t="n">
-        <v>201.3129</v>
+        <v>118.934</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.1488</v>
+        <v>0.2166</v>
       </c>
     </row>
     <row r="59">
@@ -1531,10 +1531,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>13693.1217</v>
+        <v>11924.3565</v>
       </c>
       <c r="C59" t="n">
-        <v>273.8624</v>
+        <v>238.4871</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.055</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="60">
@@ -1550,10 +1550,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>9708.7392</v>
+        <v>2858.0145</v>
       </c>
       <c r="C60" t="n">
-        <v>194.1748</v>
+        <v>57.1603</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.0542</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="61">
@@ -1569,10 +1569,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>11459.5199</v>
+        <v>8902.1504</v>
       </c>
       <c r="C61" t="n">
-        <v>229.1904</v>
+        <v>178.043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.0549</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="62">
@@ -1588,10 +1588,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>8977.804700000001</v>
+        <v>6326.46</v>
       </c>
       <c r="C62" t="n">
-        <v>179.5561</v>
+        <v>126.5292</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1518</v>
+        <v>0.1948</v>
       </c>
     </row>
     <row r="63">
@@ -1607,10 +1607,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>13348.992</v>
+        <v>10848.992</v>
       </c>
       <c r="C63" t="n">
-        <v>266.9798</v>
+        <v>216.9798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.0643</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="64">
@@ -1626,10 +1626,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>8693.489100000001</v>
+        <v>4736.6535</v>
       </c>
       <c r="C64" t="n">
-        <v>173.8698</v>
+        <v>94.73309999999999</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0634</v>
+        <v>0.0552</v>
       </c>
     </row>
     <row r="65">
@@ -1645,10 +1645,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>12084.0562</v>
+        <v>9482.3878</v>
       </c>
       <c r="C65" t="n">
-        <v>241.6811</v>
+        <v>189.6478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.0639</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="66">
@@ -1664,10 +1664,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>7989.7574</v>
+        <v>4632.6892</v>
       </c>
       <c r="C66" t="n">
-        <v>159.7951</v>
+        <v>92.6538</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.1805</v>
+        <v>0.1938</v>
       </c>
     </row>
     <row r="67">
@@ -1683,10 +1683,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>12203.8822</v>
+        <v>9237.902</v>
       </c>
       <c r="C67" t="n">
-        <v>244.0776</v>
+        <v>184.758</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.0595</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1702,10 +1702,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>8429.9679</v>
+        <v>5223.333</v>
       </c>
       <c r="C68" t="n">
-        <v>168.5994</v>
+        <v>104.4667</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.0518</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="69">
@@ -1721,10 +1721,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>7435.2991</v>
+        <v>2677.8672</v>
       </c>
       <c r="C69" t="n">
-        <v>148.706</v>
+        <v>53.5573</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.0491</v>
+        <v>0.0631</v>
       </c>
     </row>
     <row r="70">
@@ -1740,10 +1740,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>8785.038500000001</v>
+        <v>5964.6998</v>
       </c>
       <c r="C70" t="n">
-        <v>175.7008</v>
+        <v>119.294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.1611</v>
+        <v>0.1975</v>
       </c>
     </row>
     <row r="71">
@@ -1759,10 +1759,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>8198.534100000001</v>
+        <v>3540.8172</v>
       </c>
       <c r="C71" t="n">
-        <v>163.9707</v>
+        <v>70.8163</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.0553</v>
+        <v>0.0644</v>
       </c>
     </row>
     <row r="72">
@@ -1778,10 +1778,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>8388.860500000001</v>
+        <v>4985.8789</v>
       </c>
       <c r="C72" t="n">
-        <v>167.7772</v>
+        <v>99.7176</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.0503</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="73">
@@ -1797,10 +1797,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>9316.5157</v>
+        <v>6814.1427</v>
       </c>
       <c r="C73" t="n">
-        <v>186.3303</v>
+        <v>136.2829</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.0528</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="74">
@@ -1816,10 +1816,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>8387.179899999999</v>
+        <v>4367.448</v>
       </c>
       <c r="C74" t="n">
-        <v>167.7436</v>
+        <v>87.349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.161</v>
+        <v>0.1926</v>
       </c>
     </row>
     <row r="75">
@@ -1835,10 +1835,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>8044.5651</v>
+        <v>3511.7457</v>
       </c>
       <c r="C75" t="n">
-        <v>160.8913</v>
+        <v>70.2349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.0545</v>
+        <v>0.0624</v>
       </c>
     </row>
     <row r="76">
@@ -1854,10 +1854,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>7772.6802</v>
+        <v>3664.2733</v>
       </c>
       <c r="C76" t="n">
-        <v>155.4536</v>
+        <v>73.2855</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0558</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="77">
@@ -1873,10 +1873,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>10389.1262</v>
+        <v>4252.026</v>
       </c>
       <c r="C77" t="n">
-        <v>207.7825</v>
+        <v>85.04049999999999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.0588</v>
+        <v>0.06519999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -1892,10 +1892,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>8548.3174</v>
+        <v>5351.3138</v>
       </c>
       <c r="C78" t="n">
-        <v>170.9663</v>
+        <v>107.0263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.1674</v>
+        <v>0.1944</v>
       </c>
     </row>
     <row r="79">
@@ -1911,10 +1911,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>7711.6812</v>
+        <v>2703.0155</v>
       </c>
       <c r="C79" t="n">
-        <v>154.2336</v>
+        <v>54.0603</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0476</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="80">
@@ -1930,10 +1930,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>8330.164500000001</v>
+        <v>5345.5532</v>
       </c>
       <c r="C80" t="n">
-        <v>166.6033</v>
+        <v>106.9111</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0535</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="81">
@@ -1949,10 +1949,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>11743.4264</v>
+        <v>6599.1783</v>
       </c>
       <c r="C81" t="n">
-        <v>234.8685</v>
+        <v>131.9836</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0603</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -1968,10 +1968,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>6507.7171</v>
+        <v>2898.6952</v>
       </c>
       <c r="C82" t="n">
-        <v>130.1543</v>
+        <v>57.9739</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1637</v>
+        <v>0.1983</v>
       </c>
     </row>
     <row r="83">
@@ -1987,10 +1987,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>8208.8012</v>
+        <v>4932.9918</v>
       </c>
       <c r="C83" t="n">
-        <v>164.176</v>
+        <v>98.6598</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.0582</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="84">
@@ -2006,10 +2006,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>11491.8029</v>
+        <v>8991.802900000001</v>
       </c>
       <c r="C84" t="n">
-        <v>229.8361</v>
+        <v>179.8361</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0692</v>
       </c>
     </row>
     <row r="85">
@@ -2025,10 +2025,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>8922.559999999999</v>
+        <v>5997.6631</v>
       </c>
       <c r="C85" t="n">
-        <v>178.4512</v>
+        <v>119.9533</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.0677</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="86">
@@ -2044,10 +2044,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>10892.05</v>
+        <v>8189.9575</v>
       </c>
       <c r="C86" t="n">
-        <v>217.841</v>
+        <v>163.7992</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.1753</v>
+        <v>0.1972</v>
       </c>
     </row>
     <row r="87">
@@ -2063,10 +2063,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>9446.102800000001</v>
+        <v>6946.1028</v>
       </c>
       <c r="C87" t="n">
-        <v>188.9221</v>
+        <v>138.9221</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0636</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="88">
@@ -2082,10 +2082,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>7998.5287</v>
+        <v>4188.9031</v>
       </c>
       <c r="C88" t="n">
-        <v>159.9706</v>
+        <v>83.77809999999999</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0563</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -2101,10 +2101,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>8909.1306</v>
+        <v>6102.4781</v>
       </c>
       <c r="C89" t="n">
-        <v>178.1826</v>
+        <v>122.0496</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -2120,10 +2120,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>6613.5944</v>
+        <v>1603.6538</v>
       </c>
       <c r="C90" t="n">
-        <v>132.2719</v>
+        <v>32.0731</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.1574</v>
+        <v>0.1874</v>
       </c>
     </row>
     <row r="91">
@@ -2139,10 +2139,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>10893.5172</v>
+        <v>8392.9148</v>
       </c>
       <c r="C91" t="n">
-        <v>217.8703</v>
+        <v>167.8583</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.0555</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="92">
@@ -2158,10 +2158,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>9304.688099999999</v>
+        <v>3168.6924</v>
       </c>
       <c r="C92" t="n">
-        <v>186.0938</v>
+        <v>63.3738</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.0506</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="93">
@@ -2177,10 +2177,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>10623.2335</v>
+        <v>5667.1766</v>
       </c>
       <c r="C93" t="n">
-        <v>212.4647</v>
+        <v>113.3435</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.0586</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="94">
@@ -2196,10 +2196,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>9894.751</v>
+        <v>7237.2948</v>
       </c>
       <c r="C94" t="n">
-        <v>197.895</v>
+        <v>144.7459</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.1764</v>
+        <v>0.1989</v>
       </c>
     </row>
     <row r="95">
@@ -2215,10 +2215,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>7700.954</v>
+        <v>3593.5322</v>
       </c>
       <c r="C95" t="n">
-        <v>154.0191</v>
+        <v>71.8706</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0524</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="96">
@@ -2234,10 +2234,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>10436.4524</v>
+        <v>4708.6924</v>
       </c>
       <c r="C96" t="n">
-        <v>208.729</v>
+        <v>94.1738</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.0598</v>
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -2253,10 +2253,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>8821.6697</v>
+        <v>5265.2007</v>
       </c>
       <c r="C97" t="n">
-        <v>176.4334</v>
+        <v>105.304</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.062</v>
+        <v>0.0646</v>
       </c>
     </row>
     <row r="98">
@@ -2272,10 +2272,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>12379.3198</v>
+        <v>8781.469999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>247.5864</v>
+        <v>175.6294</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.1612</v>
+        <v>0.1949</v>
       </c>
     </row>
     <row r="99">
@@ -2291,10 +2291,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>7839.3347</v>
+        <v>4195.2591</v>
       </c>
       <c r="C99" t="n">
-        <v>156.7867</v>
+        <v>83.90519999999999</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.056</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="100">
@@ -2310,10 +2310,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>8983.989799999999</v>
+        <v>6273.2391</v>
       </c>
       <c r="C100" t="n">
-        <v>179.6798</v>
+        <v>125.4648</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.0615</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="101">
@@ -2329,10 +2329,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>8932.358</v>
+        <v>4973.8423</v>
       </c>
       <c r="C101" t="n">
-        <v>178.6472</v>
+        <v>99.4768</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0569</v>
+        <v>0.0645</v>
       </c>
     </row>
   </sheetData>
